--- a/grupos/6BLCM - Estadisticos 20222.xlsx
+++ b/grupos/6BLCM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="147">
   <si>
     <t>Materia</t>
   </si>
@@ -189,30 +189,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>TEMAS DE CIENCIAS DE LA SALUD</t>
-  </si>
-  <si>
-    <t>TEMAS DE FÍSICA</t>
-  </si>
-  <si>
-    <t>LITERATURA</t>
-  </si>
-  <si>
-    <t>INTRODUCCIÓN AL DERECHO</t>
-  </si>
-  <si>
-    <t>HISTORIA</t>
-  </si>
-  <si>
-    <t>TEMAS DE CIENCIAS SOCIALES</t>
+    <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
     <t>Desc Desc Desc</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -228,6 +210,15 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ARANTZA</t>
+  </si>
+  <si>
     <t>ALTAMIRANO</t>
   </si>
   <si>
@@ -285,15 +276,9 @@
     <t>NAVARRO</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>ROSAS</t>
   </si>
   <si>
@@ -451,9 +436,6 @@
   </si>
   <si>
     <t>SAMANTHA</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
   </si>
   <si>
     <t>DIANA SARAY</t>
@@ -972,7 +954,7 @@
         <v>8</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>10</v>
@@ -1026,7 +1008,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1049,7 +1031,7 @@
         <v>10</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F5">
         <v>10</v>
@@ -1103,7 +1085,7 @@
         <v>10</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -1126,7 +1108,7 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -1180,7 +1162,7 @@
         <v>10</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1203,7 +1185,7 @@
         <v>10</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F7">
         <v>10</v>
@@ -1257,7 +1239,7 @@
         <v>10</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1280,7 +1262,7 @@
         <v>10</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F8">
         <v>10</v>
@@ -1334,7 +1316,7 @@
         <v>10</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1357,7 +1339,7 @@
         <v>9</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F9">
         <v>10</v>
@@ -1411,7 +1393,7 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -1434,7 +1416,7 @@
         <v>10</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F10">
         <v>10</v>
@@ -1488,7 +1470,7 @@
         <v>10</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1511,7 +1493,7 @@
         <v>10</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -1565,7 +1547,7 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1588,7 +1570,7 @@
         <v>9</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F12">
         <v>10</v>
@@ -1642,7 +1624,7 @@
         <v>9</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1665,7 +1647,7 @@
         <v>9</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F13">
         <v>10</v>
@@ -1719,7 +1701,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1742,7 +1724,7 @@
         <v>10</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F14">
         <v>10</v>
@@ -1796,7 +1778,7 @@
         <v>10</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1819,7 +1801,7 @@
         <v>8</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F15">
         <v>10</v>
@@ -1873,7 +1855,7 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -1896,7 +1878,7 @@
         <v>10</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F16">
         <v>10</v>
@@ -1950,7 +1932,7 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -1973,7 +1955,7 @@
         <v>9</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F17">
         <v>10</v>
@@ -2027,7 +2009,7 @@
         <v>9</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>10</v>
@@ -2050,7 +2032,7 @@
         <v>10</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F18">
         <v>10</v>
@@ -2104,7 +2086,7 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -2127,7 +2109,7 @@
         <v>9</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F19">
         <v>10</v>
@@ -2181,7 +2163,7 @@
         <v>9</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>10</v>
@@ -2204,7 +2186,7 @@
         <v>10</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F20">
         <v>10</v>
@@ -2258,7 +2240,7 @@
         <v>10</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -2281,7 +2263,7 @@
         <v>8</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F21">
         <v>8</v>
@@ -2335,7 +2317,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2358,7 +2340,7 @@
         <v>10</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F22">
         <v>10</v>
@@ -2412,7 +2394,7 @@
         <v>10</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2435,7 +2417,7 @@
         <v>10</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F23">
         <v>10</v>
@@ -2489,7 +2471,7 @@
         <v>10</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2512,7 +2494,7 @@
         <v>10</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F24">
         <v>10</v>
@@ -2566,7 +2548,7 @@
         <v>10</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2589,7 +2571,7 @@
         <v>10</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F25">
         <v>10</v>
@@ -2643,7 +2625,7 @@
         <v>10</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2666,7 +2648,7 @@
         <v>10</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F26">
         <v>9</v>
@@ -2720,7 +2702,7 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2820,7 +2802,7 @@
         <v>9</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F28">
         <v>10</v>
@@ -2874,7 +2856,7 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2897,7 +2879,7 @@
         <v>10</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F29">
         <v>10</v>
@@ -2951,7 +2933,7 @@
         <v>10</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -2974,7 +2956,7 @@
         <v>10</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F30">
         <v>10</v>
@@ -3028,7 +3010,7 @@
         <v>10</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -3051,7 +3033,7 @@
         <v>8</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F31">
         <v>10</v>
@@ -3105,7 +3087,7 @@
         <v>8</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -3128,7 +3110,7 @@
         <v>7</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F32">
         <v>10</v>
@@ -3182,7 +3164,7 @@
         <v>7</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3205,7 +3187,7 @@
         <v>10</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F33">
         <v>10</v>
@@ -3259,7 +3241,7 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3282,7 +3264,7 @@
         <v>10</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F34">
         <v>10</v>
@@ -3336,7 +3318,7 @@
         <v>10</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -3359,7 +3341,7 @@
         <v>10</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F35">
         <v>10</v>
@@ -3413,7 +3395,7 @@
         <v>10</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3546,7 +3528,7 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>72</v>
@@ -3605,7 +3587,7 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>80</v>
@@ -3664,7 +3646,7 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F6">
         <v>80</v>
@@ -3723,7 +3705,7 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>80</v>
@@ -3782,7 +3764,7 @@
         <v>100</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>80</v>
@@ -3841,7 +3823,7 @@
         <v>100</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>80</v>
@@ -3900,7 +3882,7 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10">
         <v>80</v>
@@ -3959,7 +3941,7 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F11">
         <v>72</v>
@@ -4018,7 +4000,7 @@
         <v>100</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>76</v>
@@ -4077,7 +4059,7 @@
         <v>100</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F13">
         <v>80</v>
@@ -4136,7 +4118,7 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>68</v>
@@ -4195,7 +4177,7 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15">
         <v>64</v>
@@ -4254,7 +4236,7 @@
         <v>100</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>80</v>
@@ -4313,7 +4295,7 @@
         <v>100</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>80</v>
@@ -4372,7 +4354,7 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>80</v>
@@ -4431,7 +4413,7 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19">
         <v>68</v>
@@ -4490,7 +4472,7 @@
         <v>100</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>72</v>
@@ -4549,7 +4531,7 @@
         <v>100</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F21">
         <v>64</v>
@@ -4608,7 +4590,7 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>80</v>
@@ -4667,7 +4649,7 @@
         <v>100</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23">
         <v>64</v>
@@ -4726,7 +4708,7 @@
         <v>100</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <v>80</v>
@@ -4785,7 +4767,7 @@
         <v>100</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>68</v>
@@ -4844,7 +4826,7 @@
         <v>100</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>68</v>
@@ -4903,7 +4885,7 @@
         <v>100</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>64</v>
@@ -4962,7 +4944,7 @@
         <v>100</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28">
         <v>72</v>
@@ -5021,7 +5003,7 @@
         <v>100</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29">
         <v>80</v>
@@ -5080,7 +5062,7 @@
         <v>100</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F30">
         <v>80</v>
@@ -5139,7 +5121,7 @@
         <v>100</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F31">
         <v>80</v>
@@ -5198,7 +5180,7 @@
         <v>100</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32">
         <v>68</v>
@@ -5257,7 +5239,7 @@
         <v>100</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33">
         <v>80</v>
@@ -5316,7 +5298,7 @@
         <v>100</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F34">
         <v>80</v>
@@ -5375,7 +5357,7 @@
         <v>100</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F35">
         <v>80</v>
@@ -5432,7 +5414,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
@@ -5472,310 +5454,193 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
-        <v>62</v>
-      </c>
       <c r="C2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>90.63</v>
+      </c>
+      <c r="G2">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="H2">
+        <v>8.1</v>
       </c>
       <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
         <v>57</v>
       </c>
-      <c r="B3" t="s">
-        <v>62</v>
-      </c>
       <c r="C3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
+      <c r="F3">
+        <v>96.88</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>8.6</v>
+      </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>3.13</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>9.800000000000001</v>
+      </c>
       <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>9.4</v>
+      </c>
       <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>9.5</v>
+      </c>
       <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>9.5</v>
+      </c>
       <c r="I7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8">
-        <v>32</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>32</v>
-      </c>
-      <c r="J8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9">
-        <v>32</v>
-      </c>
-      <c r="D9">
-        <v>29</v>
-      </c>
-      <c r="E9">
-        <v>3</v>
-      </c>
-      <c r="F9">
-        <v>90.63</v>
-      </c>
-      <c r="G9">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="H9">
-        <v>8.1</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10">
-        <v>32</v>
-      </c>
-      <c r="D10">
-        <v>32</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>100</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11">
-        <v>32</v>
-      </c>
-      <c r="D11">
-        <v>32</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>100</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>9.4</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12">
-        <v>32</v>
-      </c>
-      <c r="D12">
-        <v>32</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>100</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>9.5</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13">
-        <v>32</v>
-      </c>
-      <c r="D13">
-        <v>32</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>100</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>9.5</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
+      <c r="J7">
         <v>0</v>
       </c>
     </row>
@@ -5786,7 +5651,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5795,16 +5660,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -5815,642 +5680,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920283</v>
+        <v>20330051920310</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920284</v>
-      </c>
-      <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920285</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920286</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920390</v>
-      </c>
-      <c r="B6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920290</v>
-      </c>
-      <c r="B7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" t="s">
-        <v>126</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920292</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920293</v>
-      </c>
-      <c r="B9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920294</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" t="s">
-        <v>129</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920394</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" t="s">
-        <v>130</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920295</v>
-      </c>
-      <c r="B12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" t="s">
-        <v>131</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920296</v>
-      </c>
-      <c r="B13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" t="s">
-        <v>104</v>
-      </c>
-      <c r="D13" t="s">
-        <v>132</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920297</v>
-      </c>
-      <c r="B14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" t="s">
-        <v>133</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920298</v>
-      </c>
-      <c r="B15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15" t="s">
-        <v>106</v>
-      </c>
-      <c r="D15" t="s">
-        <v>134</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920299</v>
-      </c>
-      <c r="B16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" t="s">
-        <v>107</v>
-      </c>
-      <c r="D16" t="s">
-        <v>135</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920300</v>
-      </c>
-      <c r="B17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" t="s">
-        <v>108</v>
-      </c>
-      <c r="D17" t="s">
-        <v>136</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920301</v>
-      </c>
-      <c r="B18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" t="s">
-        <v>137</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920303</v>
-      </c>
-      <c r="B19" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" t="s">
-        <v>109</v>
-      </c>
-      <c r="D19" t="s">
-        <v>138</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920208</v>
-      </c>
-      <c r="B20" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" t="s">
-        <v>139</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920304</v>
-      </c>
-      <c r="B21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" t="s">
-        <v>110</v>
-      </c>
-      <c r="D21" t="s">
-        <v>140</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920307</v>
-      </c>
-      <c r="B22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" t="s">
-        <v>111</v>
-      </c>
-      <c r="D22" t="s">
-        <v>141</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920308</v>
-      </c>
-      <c r="B23" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" t="s">
-        <v>112</v>
-      </c>
-      <c r="D23" t="s">
-        <v>142</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920309</v>
-      </c>
-      <c r="B24" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" t="s">
-        <v>113</v>
-      </c>
-      <c r="D24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920310</v>
-      </c>
-      <c r="B25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D25" t="s">
-        <v>144</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920211</v>
-      </c>
-      <c r="B26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C26" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920311</v>
-      </c>
-      <c r="B27" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" t="s">
-        <v>146</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920216</v>
-      </c>
-      <c r="B28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" t="s">
-        <v>115</v>
-      </c>
-      <c r="D28" t="s">
-        <v>147</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920312</v>
-      </c>
-      <c r="B29" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D29" t="s">
-        <v>148</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920379</v>
-      </c>
-      <c r="B30" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" t="s">
-        <v>117</v>
-      </c>
-      <c r="D30" t="s">
-        <v>149</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920313</v>
-      </c>
-      <c r="B31" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D31" t="s">
-        <v>150</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920314</v>
-      </c>
-      <c r="B32" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32" t="s">
-        <v>119</v>
-      </c>
-      <c r="D32" t="s">
-        <v>151</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920316</v>
-      </c>
-      <c r="B33" t="s">
-        <v>96</v>
-      </c>
-      <c r="C33" t="s">
-        <v>120</v>
-      </c>
-      <c r="D33" t="s">
-        <v>152</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -6469,16 +5714,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>54</v>
@@ -6486,16 +5731,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920283</v>
+        <v>20330051920310</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -6503,393 +5748,393 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920284</v>
+        <v>20330051920283</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920285</v>
+        <v>20330051920284</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920286</v>
+        <v>20330051920285</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920390</v>
+        <v>20330051920286</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920290</v>
+        <v>20330051920390</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920292</v>
+        <v>20330051920290</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920293</v>
+        <v>20330051920292</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920294</v>
+        <v>20330051920293</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920394</v>
+        <v>20330051920294</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920295</v>
+        <v>20330051920394</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920296</v>
+        <v>20330051920295</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920297</v>
+        <v>20330051920296</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920298</v>
+        <v>20330051920297</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920299</v>
+        <v>20330051920298</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920300</v>
+        <v>20330051920299</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920301</v>
+        <v>20330051920300</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920303</v>
+        <v>20330051920301</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920208</v>
+        <v>20330051920303</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920304</v>
+        <v>20330051920208</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920307</v>
+        <v>20330051920304</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920308</v>
+        <v>20330051920307</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920309</v>
+        <v>20330051920308</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920310</v>
+        <v>20330051920309</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -6897,16 +6142,16 @@
         <v>20330051920211</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -6914,16 +6159,16 @@
         <v>20330051920311</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -6931,16 +6176,16 @@
         <v>20330051920216</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -6948,16 +6193,16 @@
         <v>20330051920312</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -6965,16 +6210,16 @@
         <v>20330051920379</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -6982,16 +6227,16 @@
         <v>20330051920313</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D31" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -6999,16 +6244,16 @@
         <v>20330051920314</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -7016,16 +6261,16 @@
         <v>20330051920316</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7035,7 +6280,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7044,16 +6289,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -7070,42 +6315,42 @@
         <v>20330051920296</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920296</v>
+        <v>20330051920297</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7113,22 +6358,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920297</v>
+        <v>20330051920310</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -7136,738 +6381,25 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920297</v>
+        <v>20330051920312</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920312</v>
-      </c>
-      <c r="B6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920312</v>
-      </c>
-      <c r="B7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7" t="s">
-        <v>148</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920283</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" t="s">
-        <v>121</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920284</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D9" t="s">
-        <v>122</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920285</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920286</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D11" t="s">
-        <v>124</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920390</v>
-      </c>
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" t="s">
-        <v>125</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920290</v>
-      </c>
-      <c r="B13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920292</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920293</v>
-      </c>
-      <c r="B15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" t="s">
-        <v>128</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920294</v>
-      </c>
-      <c r="B16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D16" t="s">
-        <v>129</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920394</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" t="s">
-        <v>130</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>62</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920295</v>
-      </c>
-      <c r="B18" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D18" t="s">
-        <v>131</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920298</v>
-      </c>
-      <c r="B19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" t="s">
-        <v>106</v>
-      </c>
-      <c r="D19" t="s">
-        <v>134</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920299</v>
-      </c>
-      <c r="B20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" t="s">
-        <v>135</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920300</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>108</v>
-      </c>
-      <c r="D21" t="s">
-        <v>136</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920301</v>
-      </c>
-      <c r="B22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" t="s">
-        <v>80</v>
-      </c>
-      <c r="D22" t="s">
-        <v>137</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920303</v>
-      </c>
-      <c r="B23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" t="s">
-        <v>138</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>62</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920208</v>
-      </c>
-      <c r="B24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" t="s">
-        <v>139</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920304</v>
-      </c>
-      <c r="B25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" t="s">
-        <v>110</v>
-      </c>
-      <c r="D25" t="s">
-        <v>140</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920307</v>
-      </c>
-      <c r="B26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" t="s">
-        <v>111</v>
-      </c>
-      <c r="D26" t="s">
-        <v>141</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>62</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920308</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>112</v>
-      </c>
-      <c r="D27" t="s">
-        <v>142</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>62</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920309</v>
-      </c>
-      <c r="B28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" t="s">
-        <v>113</v>
-      </c>
-      <c r="D28" t="s">
-        <v>143</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>62</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920310</v>
-      </c>
-      <c r="B29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" t="s">
-        <v>144</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>62</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>20330051920211</v>
-      </c>
-      <c r="B30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>114</v>
-      </c>
-      <c r="D30" t="s">
-        <v>145</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>62</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>20330051920311</v>
-      </c>
-      <c r="B31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" t="s">
-        <v>92</v>
-      </c>
-      <c r="D31" t="s">
-        <v>146</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>62</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>20330051920216</v>
-      </c>
-      <c r="B32" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" t="s">
-        <v>115</v>
-      </c>
-      <c r="D32" t="s">
-        <v>147</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>62</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>20330051920379</v>
-      </c>
-      <c r="B33" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" t="s">
-        <v>117</v>
-      </c>
-      <c r="D33" t="s">
-        <v>149</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>62</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>20330051920313</v>
-      </c>
-      <c r="B34" t="s">
-        <v>94</v>
-      </c>
-      <c r="C34" t="s">
-        <v>118</v>
-      </c>
-      <c r="D34" t="s">
-        <v>150</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>62</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>20330051920314</v>
-      </c>
-      <c r="B35" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" t="s">
-        <v>119</v>
-      </c>
-      <c r="D35" t="s">
-        <v>151</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>62</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>20330051920316</v>
-      </c>
-      <c r="B36" t="s">
-        <v>96</v>
-      </c>
-      <c r="C36" t="s">
-        <v>120</v>
-      </c>
-      <c r="D36" t="s">
-        <v>152</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>62</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6BLCM - Estadisticos 20222.xlsx
+++ b/grupos/6BLCM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="147">
   <si>
     <t>Materia</t>
   </si>
@@ -210,232 +210,232 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>CARAZA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>CANSINO</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ARENZANO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>KAREN ESTEPHANY</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>CITLALLI</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
+  </si>
+  <si>
+    <t>JARED URIEL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>VALERIA ANGELY</t>
+  </si>
+  <si>
+    <t>STEPHANIE</t>
+  </si>
+  <si>
+    <t>SIARI DANAHY</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>YAMILE</t>
+  </si>
+  <si>
+    <t>ALEXA</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>ELIAN</t>
+  </si>
+  <si>
+    <t>MARIA MAGDALENA</t>
+  </si>
+  <si>
+    <t>IKER</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>IVONNE SHERLINE</t>
+  </si>
+  <si>
+    <t>LESLIE</t>
+  </si>
+  <si>
+    <t>RITA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>SAMANTHA</t>
   </si>
   <si>
     <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>CARAZA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>CANSINO</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ARENZANO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>KAREN ESTEPHANY</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>CITLALLI</t>
-  </si>
-  <si>
-    <t>AMERICA MICHELLE</t>
-  </si>
-  <si>
-    <t>JARED URIEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>VALERIA ANGELY</t>
-  </si>
-  <si>
-    <t>STEPHANIE</t>
-  </si>
-  <si>
-    <t>SIARI DANAHY</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>YAMILE</t>
-  </si>
-  <si>
-    <t>ALEXA</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>ELIAN</t>
-  </si>
-  <si>
-    <t>MARIA MAGDALENA</t>
-  </si>
-  <si>
-    <t>IKER</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>IVONNE SHERLINE</t>
-  </si>
-  <si>
-    <t>LESLIE</t>
-  </si>
-  <si>
-    <t>RITA ALEJANDRA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>SAMANTHA</t>
   </si>
   <si>
     <t>DIANA SARAY</t>
@@ -2725,7 +2725,7 @@
         <v>9</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F27">
         <v>8</v>
@@ -2779,7 +2779,7 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>8</v>
@@ -5495,25 +5495,25 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -5651,7 +5651,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5676,26 +5676,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920310</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -5731,27 +5711,27 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920310</v>
+        <v>20330051920283</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>115</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920283</v>
+        <v>20330051920284</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
         <v>92</v>
@@ -5765,13 +5745,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920284</v>
+        <v>20330051920285</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
         <v>117</v>
@@ -5782,13 +5762,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920285</v>
+        <v>20330051920286</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
         <v>118</v>
@@ -5799,13 +5779,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920286</v>
+        <v>20330051920390</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
         <v>119</v>
@@ -5816,13 +5796,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920390</v>
+        <v>20330051920290</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
         <v>120</v>
@@ -5833,10 +5813,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920290</v>
+        <v>20330051920292</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
         <v>95</v>
@@ -5850,13 +5830,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920292</v>
+        <v>20330051920293</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
         <v>122</v>
@@ -5867,13 +5847,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920293</v>
+        <v>20330051920294</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
         <v>123</v>
@@ -5884,13 +5864,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920294</v>
+        <v>20330051920394</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
         <v>124</v>
@@ -5901,13 +5881,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920394</v>
+        <v>20330051920295</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
         <v>125</v>
@@ -5918,10 +5898,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920295</v>
+        <v>20330051920296</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
         <v>98</v>
@@ -5935,10 +5915,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920296</v>
+        <v>20330051920297</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
         <v>99</v>
@@ -5952,10 +5932,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920297</v>
+        <v>20330051920298</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
         <v>100</v>
@@ -5969,10 +5949,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920298</v>
+        <v>20330051920299</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
         <v>101</v>
@@ -5986,10 +5966,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920299</v>
+        <v>20330051920300</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
         <v>102</v>
@@ -6003,13 +5983,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920300</v>
+        <v>20330051920301</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
         <v>131</v>
@@ -6020,13 +6000,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920301</v>
+        <v>20330051920303</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
         <v>132</v>
@@ -6037,13 +6017,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920303</v>
+        <v>20330051920208</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s">
         <v>133</v>
@@ -6054,13 +6034,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920208</v>
+        <v>20330051920304</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
         <v>134</v>
@@ -6071,10 +6051,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920304</v>
+        <v>20330051920307</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
         <v>105</v>
@@ -6088,10 +6068,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920307</v>
+        <v>20330051920308</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
         <v>106</v>
@@ -6105,10 +6085,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920308</v>
+        <v>20330051920309</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
         <v>107</v>
@@ -6122,13 +6102,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920309</v>
+        <v>20330051920310</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="D25" t="s">
         <v>138</v>
@@ -6142,10 +6122,10 @@
         <v>20330051920211</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
         <v>139</v>
@@ -6159,10 +6139,10 @@
         <v>20330051920311</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s">
         <v>140</v>
@@ -6176,10 +6156,10 @@
         <v>20330051920216</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
         <v>141</v>
@@ -6193,10 +6173,10 @@
         <v>20330051920312</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s">
         <v>142</v>
@@ -6210,10 +6190,10 @@
         <v>20330051920379</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
         <v>143</v>
@@ -6227,10 +6207,10 @@
         <v>20330051920313</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
         <v>144</v>
@@ -6244,10 +6224,10 @@
         <v>20330051920314</v>
       </c>
       <c r="B32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s">
         <v>145</v>
@@ -6261,10 +6241,10 @@
         <v>20330051920316</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D33" t="s">
         <v>146</v>
@@ -6280,7 +6260,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6315,13 +6295,13 @@
         <v>20330051920296</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -6338,13 +6318,13 @@
         <v>20330051920297</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6358,47 +6338,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920310</v>
+        <v>20330051920312</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>142</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G4">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920312</v>
-      </c>
-      <c r="B5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6BLCM - Estadisticos 20222.xlsx
+++ b/grupos/6BLCM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="149">
   <si>
     <t>Materia</t>
   </si>
@@ -192,10 +192,16 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
     <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
+    <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
     <t>NC</t>
@@ -5521,7 +5527,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4">
         <v>32</v>
@@ -5553,7 +5559,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5">
         <v>32</v>
@@ -5585,7 +5591,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C6">
         <v>32</v>
@@ -5617,7 +5623,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>32</v>
@@ -5660,16 +5666,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -5694,16 +5700,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>54</v>
@@ -5714,13 +5720,13 @@
         <v>20330051920283</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -5731,13 +5737,13 @@
         <v>20330051920284</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -5748,13 +5754,13 @@
         <v>20330051920285</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -5765,13 +5771,13 @@
         <v>20330051920286</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -5782,13 +5788,13 @@
         <v>20330051920390</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -5799,13 +5805,13 @@
         <v>20330051920290</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -5816,13 +5822,13 @@
         <v>20330051920292</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5833,13 +5839,13 @@
         <v>20330051920293</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -5850,13 +5856,13 @@
         <v>20330051920294</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -5867,13 +5873,13 @@
         <v>20330051920394</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -5884,13 +5890,13 @@
         <v>20330051920295</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -5901,13 +5907,13 @@
         <v>20330051920296</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -5918,13 +5924,13 @@
         <v>20330051920297</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -5935,13 +5941,13 @@
         <v>20330051920298</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -5952,13 +5958,13 @@
         <v>20330051920299</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -5969,13 +5975,13 @@
         <v>20330051920300</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -5986,13 +5992,13 @@
         <v>20330051920301</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6003,13 +6009,13 @@
         <v>20330051920303</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6020,13 +6026,13 @@
         <v>20330051920208</v>
       </c>
       <c r="B20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" t="s">
         <v>80</v>
       </c>
-      <c r="C20" t="s">
-        <v>78</v>
-      </c>
       <c r="D20" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6037,13 +6043,13 @@
         <v>20330051920304</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -6054,13 +6060,13 @@
         <v>20330051920307</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -6071,13 +6077,13 @@
         <v>20330051920308</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6088,13 +6094,13 @@
         <v>20330051920309</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -6105,13 +6111,13 @@
         <v>20330051920310</v>
       </c>
       <c r="B25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" t="s">
         <v>84</v>
       </c>
-      <c r="C25" t="s">
-        <v>82</v>
-      </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6122,13 +6128,13 @@
         <v>20330051920211</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -6139,13 +6145,13 @@
         <v>20330051920311</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D27" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -6156,13 +6162,13 @@
         <v>20330051920216</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -6173,13 +6179,13 @@
         <v>20330051920312</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -6190,13 +6196,13 @@
         <v>20330051920379</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D30" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -6207,13 +6213,13 @@
         <v>20330051920313</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D31" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -6224,13 +6230,13 @@
         <v>20330051920314</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -6241,13 +6247,13 @@
         <v>20330051920316</v>
       </c>
       <c r="B33" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -6269,16 +6275,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6295,13 +6301,13 @@
         <v>20330051920296</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -6318,13 +6324,13 @@
         <v>20330051920297</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6341,13 +6347,13 @@
         <v>20330051920312</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>

--- a/grupos/6BLCM - Estadisticos 20222.xlsx
+++ b/grupos/6BLCM - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="71">
   <si>
     <t>Materia</t>
   </si>
@@ -216,262 +215,31 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>CARAZA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>CANSINO</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
     <t>PRADO</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ARENZANO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>KAREN ESTEPHANY</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>CITLALLI</t>
-  </si>
-  <si>
-    <t>AMERICA MICHELLE</t>
-  </si>
-  <si>
-    <t>JARED URIEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>VALERIA ANGELY</t>
-  </si>
-  <si>
-    <t>STEPHANIE</t>
-  </si>
-  <si>
-    <t>SIARI DANAHY</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>YAMILE</t>
-  </si>
-  <si>
     <t>ALEXA</t>
   </si>
   <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>ELIAN</t>
-  </si>
-  <si>
-    <t>MARIA MAGDALENA</t>
-  </si>
-  <si>
-    <t>IKER</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>IVONNE SHERLINE</t>
-  </si>
-  <si>
-    <t>LESLIE</t>
-  </si>
-  <si>
-    <t>RITA ALEJANDRA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>SAMANTHA</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>DIANA SARAY</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>MARIA XIMENA</t>
-  </si>
-  <si>
     <t>NAOMI</t>
-  </si>
-  <si>
-    <t>ZULEICA RENATA</t>
-  </si>
-  <si>
-    <t>JOSELIN GUADALUPE</t>
-  </si>
-  <si>
-    <t>ANEL</t>
-  </si>
-  <si>
-    <t>LAURA IVETTE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -524,11 +292,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -969,22 +738,22 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1014,13 +783,13 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1046,22 +815,22 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1097,7 +866,7 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1123,22 +892,22 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1200,22 +969,22 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1236,22 +1005,22 @@
         <v>-1</v>
       </c>
       <c r="T7">
+        <v>8</v>
+      </c>
+      <c r="U7">
+        <v>8</v>
+      </c>
+      <c r="V7">
+        <v>10</v>
+      </c>
+      <c r="W7">
         <v>7</v>
       </c>
-      <c r="U7">
-        <v>7</v>
-      </c>
-      <c r="V7">
-        <v>10</v>
-      </c>
-      <c r="W7">
-        <v>6</v>
-      </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1277,22 +1046,22 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1328,7 +1097,7 @@
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1354,22 +1123,22 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1431,22 +1200,22 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1508,22 +1277,22 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1585,22 +1354,22 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1621,10 +1390,10 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1662,22 +1431,22 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1713,7 +1482,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1739,22 +1508,22 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1784,7 +1553,7 @@
         <v>10</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1816,22 +1585,22 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1864,7 +1633,7 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1893,22 +1662,22 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1938,7 +1707,7 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -1970,22 +1739,22 @@
         <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2006,22 +1775,22 @@
         <v>-1</v>
       </c>
       <c r="T17">
+        <v>8</v>
+      </c>
+      <c r="U17">
+        <v>8</v>
+      </c>
+      <c r="V17">
+        <v>9</v>
+      </c>
+      <c r="W17">
+        <v>8</v>
+      </c>
+      <c r="X17">
+        <v>10</v>
+      </c>
+      <c r="Y17">
         <v>7</v>
-      </c>
-      <c r="U17">
-        <v>7</v>
-      </c>
-      <c r="V17">
-        <v>9</v>
-      </c>
-      <c r="W17">
-        <v>8</v>
-      </c>
-      <c r="X17">
-        <v>10</v>
-      </c>
-      <c r="Y17">
-        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2047,22 +1816,22 @@
         <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2124,22 +1893,22 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2160,10 +1929,10 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V19">
         <v>9</v>
@@ -2175,7 +1944,7 @@
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2201,22 +1970,22 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2246,7 +2015,7 @@
         <v>10</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -2278,22 +2047,22 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2329,7 +2098,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2355,22 +2124,22 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2400,13 +2169,13 @@
         <v>10</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X22">
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2432,22 +2201,22 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2477,13 +2246,13 @@
         <v>10</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2509,22 +2278,22 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2554,7 +2323,7 @@
         <v>10</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2586,22 +2355,22 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2663,22 +2432,22 @@
         <v>7</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2708,13 +2477,13 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2740,22 +2509,22 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2776,10 +2545,10 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V27">
         <v>9</v>
@@ -2788,10 +2557,10 @@
         <v>6</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2817,22 +2586,22 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2862,13 +2631,13 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2894,22 +2663,22 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2939,7 +2708,7 @@
         <v>10</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -2971,22 +2740,22 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3007,10 +2776,10 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>10</v>
@@ -3048,22 +2817,22 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3093,7 +2862,7 @@
         <v>8</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -3125,22 +2894,22 @@
         <v>5</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3202,22 +2971,22 @@
         <v>9</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3253,7 +3022,7 @@
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3279,22 +3048,22 @@
         <v>9</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3324,13 +3093,13 @@
         <v>10</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X34">
         <v>10</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3356,22 +3125,22 @@
         <v>9</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3392,10 +3161,10 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V35">
         <v>10</v>
@@ -3407,7 +3176,7 @@
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3543,22 +3312,22 @@
         <v>80</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -3602,22 +3371,22 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -3661,22 +3430,22 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -3720,22 +3489,22 @@
         <v>92</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -3779,22 +3548,22 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -3838,22 +3607,22 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -3897,22 +3666,22 @@
         <v>96</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -3956,22 +3725,22 @@
         <v>76</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -4015,22 +3784,22 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -4074,22 +3843,22 @@
         <v>92</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -4133,22 +3902,22 @@
         <v>84</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4192,22 +3961,22 @@
         <v>76</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4251,22 +4020,22 @@
         <v>96</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4310,22 +4079,22 @@
         <v>80</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4369,22 +4138,22 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -4428,22 +4197,22 @@
         <v>92</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -4487,22 +4256,22 @@
         <v>96</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -4546,22 +4315,22 @@
         <v>76</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -4605,22 +4374,22 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -4664,22 +4433,22 @@
         <v>84</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -4723,22 +4492,22 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -4782,22 +4551,22 @@
         <v>92</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -4841,22 +4610,22 @@
         <v>100</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -4900,22 +4669,22 @@
         <v>76</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -4959,22 +4728,22 @@
         <v>92</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -5018,22 +4787,22 @@
         <v>100</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -5077,22 +4846,22 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -5136,22 +4905,22 @@
         <v>100</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -5195,22 +4964,22 @@
         <v>92</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -5254,22 +5023,22 @@
         <v>100</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -5313,22 +5082,22 @@
         <v>80</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -5372,22 +5141,22 @@
         <v>100</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -5424,6 +5193,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -5469,24 +5240,24 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>90.63</v>
-      </c>
-      <c r="G2">
-        <v>9.380000000000001</v>
+        <v>2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>93.8</v>
+      </c>
+      <c r="G2" s="2">
+        <v>6.2</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5506,19 +5277,19 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>100</v>
-      </c>
-      <c r="G3">
+      <c r="F3" s="2">
+        <v>100</v>
+      </c>
+      <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5538,19 +5309,19 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
-      <c r="G4">
+      <c r="F4" s="2">
+        <v>100</v>
+      </c>
+      <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5570,10 +5341,10 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5">
+      <c r="F5" s="2">
+        <v>100</v>
+      </c>
+      <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5">
@@ -5582,7 +5353,7 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5602,19 +5373,19 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>100</v>
-      </c>
-      <c r="G6">
+      <c r="F6" s="2">
+        <v>100</v>
+      </c>
+      <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5634,19 +5405,19 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="2">
+        <v>100</v>
+      </c>
+      <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5691,582 +5462,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>20330051920283</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>20330051920284</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>20330051920285</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>20330051920286</v>
-      </c>
-      <c r="B5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>20330051920390</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>20330051920290</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>20330051920292</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" t="s">
-        <v>123</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>20330051920293</v>
-      </c>
-      <c r="B9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" t="s">
-        <v>124</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>20330051920294</v>
-      </c>
-      <c r="B10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>20330051920394</v>
-      </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" t="s">
-        <v>126</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>20330051920295</v>
-      </c>
-      <c r="B12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" t="s">
-        <v>99</v>
-      </c>
-      <c r="D12" t="s">
-        <v>127</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>20330051920296</v>
-      </c>
-      <c r="B13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" t="s">
-        <v>128</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>20330051920297</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>20330051920298</v>
-      </c>
-      <c r="B15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D15" t="s">
-        <v>130</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>20330051920299</v>
-      </c>
-      <c r="B16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D16" t="s">
-        <v>131</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>20330051920300</v>
-      </c>
-      <c r="B17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" t="s">
-        <v>132</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>20330051920301</v>
-      </c>
-      <c r="B18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" t="s">
-        <v>133</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>20330051920303</v>
-      </c>
-      <c r="B19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" t="s">
-        <v>134</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>20330051920208</v>
-      </c>
-      <c r="B20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" t="s">
-        <v>135</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>20330051920304</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>106</v>
-      </c>
-      <c r="D21" t="s">
-        <v>136</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>20330051920307</v>
-      </c>
-      <c r="B22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" t="s">
-        <v>107</v>
-      </c>
-      <c r="D22" t="s">
-        <v>137</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>20330051920308</v>
-      </c>
-      <c r="B23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>108</v>
-      </c>
-      <c r="D23" t="s">
-        <v>138</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>20330051920309</v>
-      </c>
-      <c r="B24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" t="s">
-        <v>109</v>
-      </c>
-      <c r="D24" t="s">
-        <v>139</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>20330051920310</v>
-      </c>
-      <c r="B25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" t="s">
-        <v>140</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>20330051920211</v>
-      </c>
-      <c r="B26" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" t="s">
-        <v>141</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>20330051920311</v>
-      </c>
-      <c r="B27" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" t="s">
-        <v>88</v>
-      </c>
-      <c r="D27" t="s">
-        <v>142</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>20330051920216</v>
-      </c>
-      <c r="B28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" t="s">
-        <v>143</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>20330051920312</v>
-      </c>
-      <c r="B29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" t="s">
-        <v>144</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>20330051920379</v>
-      </c>
-      <c r="B30" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" t="s">
-        <v>113</v>
-      </c>
-      <c r="D30" t="s">
-        <v>145</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>20330051920313</v>
-      </c>
-      <c r="B31" t="s">
-        <v>90</v>
-      </c>
-      <c r="C31" t="s">
-        <v>114</v>
-      </c>
-      <c r="D31" t="s">
-        <v>146</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>20330051920314</v>
-      </c>
-      <c r="B32" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" t="s">
-        <v>115</v>
-      </c>
-      <c r="D32" t="s">
-        <v>147</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>20330051920316</v>
-      </c>
-      <c r="B33" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" t="s">
-        <v>116</v>
-      </c>
-      <c r="D33" t="s">
-        <v>148</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6301,13 +5497,13 @@
         <v>20330051920296</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -6321,16 +5517,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920297</v>
+        <v>20330051920312</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6339,29 +5535,6 @@
         <v>56</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920312</v>
-      </c>
-      <c r="B4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6BLCM - Estadisticos 20222.xlsx
+++ b/grupos/6BLCM - Estadisticos 20222.xlsx
@@ -744,7 +744,7 @@
         <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>9</v>
@@ -780,7 +780,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -821,7 +821,7 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -898,7 +898,7 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -975,7 +975,7 @@
         <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>7</v>
@@ -1011,7 +1011,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>7</v>
@@ -1052,7 +1052,7 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -1129,7 +1129,7 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>10</v>
@@ -1206,7 +1206,7 @@
         <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>7</v>
@@ -1242,7 +1242,7 @@
         <v>10</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1283,7 +1283,7 @@
         <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>9</v>
@@ -1360,7 +1360,7 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
         <v>10</v>
@@ -1437,7 +1437,7 @@
         <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
         <v>9</v>
@@ -1514,7 +1514,7 @@
         <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
         <v>9</v>
@@ -1591,7 +1591,7 @@
         <v>7</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>6</v>
@@ -1627,7 +1627,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -1668,7 +1668,7 @@
         <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
         <v>10</v>
@@ -1745,7 +1745,7 @@
         <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
         <v>8</v>
@@ -1781,7 +1781,7 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -1822,7 +1822,7 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>10</v>
@@ -1899,7 +1899,7 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
         <v>8</v>
@@ -1976,7 +1976,7 @@
         <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
         <v>10</v>
@@ -2053,7 +2053,7 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
         <v>6</v>
@@ -2130,7 +2130,7 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
         <v>10</v>
@@ -2166,7 +2166,7 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -2207,7 +2207,7 @@
         <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
         <v>10</v>
@@ -2284,7 +2284,7 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
         <v>10</v>
@@ -2320,7 +2320,7 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>9</v>
@@ -2361,7 +2361,7 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
         <v>7</v>
@@ -2397,7 +2397,7 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>7</v>
@@ -2438,7 +2438,7 @@
         <v>8</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>9</v>
@@ -2515,7 +2515,7 @@
         <v>8</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
         <v>6</v>
@@ -2551,7 +2551,7 @@
         <v>9</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>6</v>
@@ -2592,7 +2592,7 @@
         <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
         <v>6</v>
@@ -2628,7 +2628,7 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -2669,7 +2669,7 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
         <v>10</v>
@@ -2746,7 +2746,7 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
         <v>10</v>
@@ -2823,7 +2823,7 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
         <v>10</v>
@@ -2859,7 +2859,7 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -2900,7 +2900,7 @@
         <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
         <v>9</v>
@@ -2936,7 +2936,7 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>9</v>
@@ -2977,7 +2977,7 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
         <v>10</v>
@@ -3054,7 +3054,7 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
         <v>10</v>
@@ -3131,7 +3131,7 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
         <v>10</v>
@@ -3318,7 +3318,7 @@
         <v>110</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K4">
         <v>100</v>
@@ -3377,7 +3377,7 @@
         <v>120</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5">
         <v>100</v>
@@ -3436,7 +3436,7 @@
         <v>110</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -3495,7 +3495,7 @@
         <v>115</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K7">
         <v>100</v>
@@ -3554,7 +3554,7 @@
         <v>115</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8">
         <v>100</v>
@@ -3613,7 +3613,7 @@
         <v>115</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -3672,7 +3672,7 @@
         <v>110</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>100</v>
@@ -3731,7 +3731,7 @@
         <v>110</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -3790,7 +3790,7 @@
         <v>120</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -3849,7 +3849,7 @@
         <v>120</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -3908,7 +3908,7 @@
         <v>110</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -3967,7 +3967,7 @@
         <v>110</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -4026,7 +4026,7 @@
         <v>120</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16">
         <v>100</v>
@@ -4085,7 +4085,7 @@
         <v>120</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K17">
         <v>100</v>
@@ -4144,7 +4144,7 @@
         <v>120</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K18">
         <v>100</v>
@@ -4203,7 +4203,7 @@
         <v>120</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -4262,7 +4262,7 @@
         <v>110</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20">
         <v>100</v>
@@ -4321,7 +4321,7 @@
         <v>120</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K21">
         <v>100</v>
@@ -4380,7 +4380,7 @@
         <v>120</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22">
         <v>100</v>
@@ -4439,7 +4439,7 @@
         <v>110</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23">
         <v>100</v>
@@ -4498,7 +4498,7 @@
         <v>120</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -4557,7 +4557,7 @@
         <v>120</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -4616,7 +4616,7 @@
         <v>110</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K26">
         <v>100</v>
@@ -4675,7 +4675,7 @@
         <v>110</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -4734,7 +4734,7 @@
         <v>120</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28">
         <v>100</v>
@@ -4793,7 +4793,7 @@
         <v>120</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -4852,7 +4852,7 @@
         <v>120</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -4911,7 +4911,7 @@
         <v>120</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -4970,7 +4970,7 @@
         <v>120</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -5029,7 +5029,7 @@
         <v>120</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K33">
         <v>100</v>
@@ -5088,7 +5088,7 @@
         <v>120</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K34">
         <v>100</v>
@@ -5147,7 +5147,7 @@
         <v>120</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K35">
         <v>100</v>
@@ -5348,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>

--- a/grupos/6BLCM - Estadisticos 20222.xlsx
+++ b/grupos/6BLCM - Estadisticos 20222.xlsx
@@ -3306,16 +3306,16 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G4">
         <v>80</v>
       </c>
       <c r="H4">
-        <v>115</v>
+        <v>97.7</v>
       </c>
       <c r="I4">
-        <v>110</v>
+        <v>95.5</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -3324,28 +3324,28 @@
         <v>100</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="M4">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3365,16 +3365,16 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>100</v>
       </c>
       <c r="H5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -3386,25 +3386,25 @@
         <v>100</v>
       </c>
       <c r="M5">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3424,16 +3424,16 @@
         <v>100</v>
       </c>
       <c r="F6">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>100</v>
       </c>
       <c r="H6">
-        <v>115</v>
+        <v>97.7</v>
       </c>
       <c r="I6">
-        <v>110</v>
+        <v>95.5</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3448,22 +3448,22 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3483,16 +3483,16 @@
         <v>100</v>
       </c>
       <c r="F7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>92</v>
       </c>
       <c r="H7">
-        <v>115</v>
+        <v>97.7</v>
       </c>
       <c r="I7">
-        <v>115</v>
+        <v>97.7</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -3504,25 +3504,25 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3542,16 +3542,16 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>100</v>
       </c>
       <c r="H8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I8">
-        <v>115</v>
+        <v>97.7</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -3566,22 +3566,22 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3601,16 +3601,16 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>100</v>
       </c>
       <c r="H9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I9">
-        <v>115</v>
+        <v>97.7</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -3622,25 +3622,25 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3660,16 +3660,16 @@
         <v>100</v>
       </c>
       <c r="F10">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>96</v>
       </c>
       <c r="H10">
-        <v>115</v>
+        <v>97.7</v>
       </c>
       <c r="I10">
-        <v>110</v>
+        <v>95.5</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -3681,25 +3681,25 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3719,16 +3719,16 @@
         <v>100</v>
       </c>
       <c r="F11">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G11">
         <v>76</v>
       </c>
       <c r="H11">
-        <v>112.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I11">
-        <v>110</v>
+        <v>95.5</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -3737,28 +3737,28 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="M11">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3778,16 +3778,16 @@
         <v>100</v>
       </c>
       <c r="F12">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="G12">
         <v>100</v>
       </c>
       <c r="H12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -3796,28 +3796,28 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="M12">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3837,16 +3837,16 @@
         <v>100</v>
       </c>
       <c r="F13">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>92</v>
       </c>
       <c r="H13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J13">
         <v>100</v>
@@ -3858,25 +3858,25 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3896,16 +3896,16 @@
         <v>100</v>
       </c>
       <c r="F14">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="G14">
         <v>84</v>
       </c>
       <c r="H14">
-        <v>115</v>
+        <v>97.7</v>
       </c>
       <c r="I14">
-        <v>110</v>
+        <v>95.5</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -3914,28 +3914,28 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="M14">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3955,16 +3955,16 @@
         <v>100</v>
       </c>
       <c r="F15">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="G15">
         <v>76</v>
       </c>
       <c r="H15">
-        <v>112.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I15">
-        <v>110</v>
+        <v>95.5</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -3973,28 +3973,28 @@
         <v>100</v>
       </c>
       <c r="L15">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M15">
         <v>72</v>
       </c>
-      <c r="M15">
-        <v>68</v>
-      </c>
       <c r="N15">
-        <v>0</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4014,16 +4014,16 @@
         <v>100</v>
       </c>
       <c r="F16">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G16">
         <v>96</v>
       </c>
       <c r="H16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -4038,22 +4038,22 @@
         <v>96</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4073,16 +4073,16 @@
         <v>100</v>
       </c>
       <c r="F17">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G17">
         <v>80</v>
       </c>
       <c r="H17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J17">
         <v>100</v>
@@ -4094,25 +4094,25 @@
         <v>100</v>
       </c>
       <c r="M17">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4132,16 +4132,16 @@
         <v>100</v>
       </c>
       <c r="F18">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G18">
         <v>100</v>
       </c>
       <c r="H18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J18">
         <v>100</v>
@@ -4153,25 +4153,25 @@
         <v>100</v>
       </c>
       <c r="M18">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4191,16 +4191,16 @@
         <v>100</v>
       </c>
       <c r="F19">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="G19">
         <v>92</v>
       </c>
       <c r="H19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J19">
         <v>100</v>
@@ -4209,28 +4209,28 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="M19">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4250,16 +4250,16 @@
         <v>100</v>
       </c>
       <c r="F20">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G20">
         <v>96</v>
       </c>
       <c r="H20">
-        <v>112.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I20">
-        <v>110</v>
+        <v>95.5</v>
       </c>
       <c r="J20">
         <v>100</v>
@@ -4268,28 +4268,28 @@
         <v>100</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="M20">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4309,16 +4309,16 @@
         <v>100</v>
       </c>
       <c r="F21">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="G21">
         <v>76</v>
       </c>
       <c r="H21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J21">
         <v>100</v>
@@ -4327,28 +4327,28 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="M21">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4368,16 +4368,16 @@
         <v>100</v>
       </c>
       <c r="F22">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G22">
         <v>100</v>
       </c>
       <c r="H22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J22">
         <v>100</v>
@@ -4389,25 +4389,25 @@
         <v>100</v>
       </c>
       <c r="M22">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4427,16 +4427,16 @@
         <v>100</v>
       </c>
       <c r="F23">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="G23">
         <v>84</v>
       </c>
       <c r="H23">
-        <v>115</v>
+        <v>97.7</v>
       </c>
       <c r="I23">
-        <v>110</v>
+        <v>95.5</v>
       </c>
       <c r="J23">
         <v>100</v>
@@ -4445,28 +4445,28 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="M23">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4486,16 +4486,16 @@
         <v>100</v>
       </c>
       <c r="F24">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G24">
         <v>100</v>
       </c>
       <c r="H24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J24">
         <v>100</v>
@@ -4510,22 +4510,22 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4545,16 +4545,16 @@
         <v>100</v>
       </c>
       <c r="F25">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="G25">
         <v>92</v>
       </c>
       <c r="H25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J25">
         <v>100</v>
@@ -4563,28 +4563,28 @@
         <v>100</v>
       </c>
       <c r="L25">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="M25">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4604,16 +4604,16 @@
         <v>100</v>
       </c>
       <c r="F26">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="G26">
         <v>100</v>
       </c>
       <c r="H26">
-        <v>112.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I26">
-        <v>110</v>
+        <v>95.5</v>
       </c>
       <c r="J26">
         <v>100</v>
@@ -4622,28 +4622,28 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="M26">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4663,16 +4663,16 @@
         <v>100</v>
       </c>
       <c r="F27">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="G27">
         <v>76</v>
       </c>
       <c r="H27">
-        <v>112.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I27">
-        <v>110</v>
+        <v>95.5</v>
       </c>
       <c r="J27">
         <v>100</v>
@@ -4681,28 +4681,28 @@
         <v>100</v>
       </c>
       <c r="L27">
-        <v>100</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="M27">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4722,16 +4722,16 @@
         <v>100</v>
       </c>
       <c r="F28">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G28">
         <v>92</v>
       </c>
       <c r="H28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J28">
         <v>100</v>
@@ -4740,28 +4740,28 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="M28">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4781,16 +4781,16 @@
         <v>100</v>
       </c>
       <c r="F29">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G29">
         <v>100</v>
       </c>
       <c r="H29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J29">
         <v>100</v>
@@ -4802,25 +4802,25 @@
         <v>100</v>
       </c>
       <c r="M29">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4840,16 +4840,16 @@
         <v>100</v>
       </c>
       <c r="F30">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G30">
         <v>100</v>
       </c>
       <c r="H30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -4861,25 +4861,25 @@
         <v>100</v>
       </c>
       <c r="M30">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4899,16 +4899,16 @@
         <v>100</v>
       </c>
       <c r="F31">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G31">
         <v>100</v>
       </c>
       <c r="H31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J31">
         <v>100</v>
@@ -4920,25 +4920,25 @@
         <v>100</v>
       </c>
       <c r="M31">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -4958,16 +4958,16 @@
         <v>100</v>
       </c>
       <c r="F32">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="G32">
         <v>92</v>
       </c>
       <c r="H32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J32">
         <v>100</v>
@@ -4976,28 +4976,28 @@
         <v>100</v>
       </c>
       <c r="L32">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="M32">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5017,16 +5017,16 @@
         <v>100</v>
       </c>
       <c r="F33">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G33">
         <v>100</v>
       </c>
       <c r="H33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J33">
         <v>100</v>
@@ -5038,25 +5038,25 @@
         <v>100</v>
       </c>
       <c r="M33">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5076,16 +5076,16 @@
         <v>100</v>
       </c>
       <c r="F34">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G34">
         <v>80</v>
       </c>
       <c r="H34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J34">
         <v>100</v>
@@ -5097,25 +5097,25 @@
         <v>100</v>
       </c>
       <c r="M34">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5135,16 +5135,16 @@
         <v>100</v>
       </c>
       <c r="F35">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G35">
         <v>100</v>
       </c>
       <c r="H35">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I35">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J35">
         <v>100</v>
@@ -5156,25 +5156,25 @@
         <v>100</v>
       </c>
       <c r="M35">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6BLCM - Estadisticos 20222.xlsx
+++ b/grupos/6BLCM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="65">
   <si>
     <t>Materia</t>
   </si>
@@ -213,24 +213,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ALEXA</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
   </si>
 </sst>
 </file>
@@ -756,22 +738,22 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -780,10 +762,10 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -833,22 +815,22 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -910,22 +892,22 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -943,7 +925,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -987,22 +969,22 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -1014,7 +996,7 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>9</v>
@@ -1064,22 +1046,22 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1097,7 +1079,7 @@
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1141,22 +1123,22 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1174,7 +1156,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1218,40 +1200,40 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1295,22 +1277,22 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1319,7 +1301,7 @@
         <v>9</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1372,22 +1354,22 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1449,22 +1431,22 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1526,22 +1508,22 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1559,7 +1541,7 @@
         <v>10</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1603,40 +1585,40 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>7</v>
       </c>
       <c r="W15">
+        <v>7</v>
+      </c>
+      <c r="X15">
+        <v>8</v>
+      </c>
+      <c r="Y15">
         <v>6</v>
-      </c>
-      <c r="X15">
-        <v>8</v>
-      </c>
-      <c r="Y15">
-        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1680,22 +1662,22 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1704,7 +1686,7 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -1757,25 +1739,25 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -1784,7 +1766,7 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>10</v>
@@ -1834,22 +1816,22 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -1911,22 +1893,22 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -1938,13 +1920,13 @@
         <v>9</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1988,22 +1970,22 @@
         <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2021,7 +2003,7 @@
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2065,22 +2047,22 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2092,13 +2074,13 @@
         <v>8</v>
       </c>
       <c r="W21">
+        <v>6</v>
+      </c>
+      <c r="X21">
+        <v>9</v>
+      </c>
+      <c r="Y21">
         <v>7</v>
-      </c>
-      <c r="X21">
-        <v>8</v>
-      </c>
-      <c r="Y21">
-        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2142,22 +2124,22 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2219,22 +2201,22 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2296,22 +2278,22 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2373,22 +2355,22 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2450,31 +2432,31 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>9</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2527,22 +2509,22 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -2554,13 +2536,13 @@
         <v>8</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2598,28 +2580,28 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M28">
         <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -2628,16 +2610,16 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2681,22 +2663,22 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -2758,22 +2740,22 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -2835,22 +2817,22 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -2859,7 +2841,7 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -2912,22 +2894,22 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -2945,7 +2927,7 @@
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -2989,22 +2971,22 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3013,7 +2995,7 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3066,22 +3048,22 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3143,22 +3125,22 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3330,10 +3312,10 @@
         <v>76</v>
       </c>
       <c r="N4">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O4">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -3342,10 +3324,10 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>95.59999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="S4">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3404,7 +3386,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>94</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3448,10 +3430,10 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O6">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -3507,10 +3489,10 @@
         <v>90</v>
       </c>
       <c r="N7">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O7">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -3522,7 +3504,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3569,7 +3551,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -3628,7 +3610,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -3640,7 +3622,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>96</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3684,10 +3666,10 @@
         <v>88</v>
       </c>
       <c r="N10">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O10">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -3699,7 +3681,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>88</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3743,10 +3725,10 @@
         <v>80</v>
       </c>
       <c r="N11">
-        <v>96.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O11">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -3755,10 +3737,10 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>95.59999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="S11">
-        <v>80</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3802,7 +3784,7 @@
         <v>94</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -3814,10 +3796,10 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>97.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S12">
-        <v>94</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3876,7 +3858,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>94</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3920,10 +3902,10 @@
         <v>86</v>
       </c>
       <c r="N14">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O14">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -3932,10 +3914,10 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>93.3</v>
+        <v>95.7</v>
       </c>
       <c r="S14">
-        <v>86</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3979,10 +3961,10 @@
         <v>72</v>
       </c>
       <c r="N15">
-        <v>96.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="O15">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -3991,10 +3973,10 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>75.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="S15">
-        <v>72</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4053,7 +4035,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>96</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4097,7 +4079,7 @@
         <v>82</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -4112,7 +4094,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>82</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4171,7 +4153,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>96</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4227,10 +4209,10 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>93.3</v>
+        <v>95.7</v>
       </c>
       <c r="S19">
-        <v>88</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4274,10 +4256,10 @@
         <v>86</v>
       </c>
       <c r="N20">
-        <v>96.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O20">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -4286,10 +4268,10 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>95.59999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="S20">
-        <v>86</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4345,10 +4327,10 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>91.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="S21">
-        <v>74</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4407,7 +4389,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>94</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4451,10 +4433,10 @@
         <v>86</v>
       </c>
       <c r="N23">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O23">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -4463,10 +4445,10 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>91.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="S23">
-        <v>86</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4581,10 +4563,10 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>93.3</v>
+        <v>95.7</v>
       </c>
       <c r="S25">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4628,10 +4610,10 @@
         <v>88</v>
       </c>
       <c r="N26">
-        <v>96.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="O26">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -4640,10 +4622,10 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>93.3</v>
+        <v>95.7</v>
       </c>
       <c r="S26">
-        <v>88</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4687,10 +4669,10 @@
         <v>78</v>
       </c>
       <c r="N27">
-        <v>96.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="O27">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P27">
         <v>100</v>
@@ -4699,10 +4681,10 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>91.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="S27">
-        <v>78</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4758,10 +4740,10 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>95.59999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="S28">
-        <v>86</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4820,7 +4802,7 @@
         <v>100</v>
       </c>
       <c r="S29">
-        <v>94</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4879,7 +4861,7 @@
         <v>100</v>
       </c>
       <c r="S30">
-        <v>98</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4938,7 +4920,7 @@
         <v>100</v>
       </c>
       <c r="S31">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -4994,10 +4976,10 @@
         <v>100</v>
       </c>
       <c r="R32">
-        <v>93.3</v>
+        <v>95.7</v>
       </c>
       <c r="S32">
-        <v>86</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5056,7 +5038,7 @@
         <v>100</v>
       </c>
       <c r="S33">
-        <v>98</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5115,7 +5097,7 @@
         <v>100</v>
       </c>
       <c r="S34">
-        <v>88</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5174,7 +5156,7 @@
         <v>100</v>
       </c>
       <c r="S35">
-        <v>98</v>
+        <v>98.8</v>
       </c>
     </row>
   </sheetData>
@@ -5240,19 +5222,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5284,7 +5266,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5316,7 +5298,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5348,7 +5330,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5380,7 +5362,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5462,7 +5444,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5492,52 +5474,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920296</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920312</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
